--- a/Sajjad data/by_country_and_state/USA/OR.xlsx
+++ b/Sajjad data/by_country_and_state/USA/OR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="433">
   <si>
     <t>Business Name</t>
   </si>
@@ -368,6 +368,948 @@
   </si>
   <si>
     <t>2026-10-25T16:28:47.220Z</t>
+  </si>
+  <si>
+    <t>Dustin A. Wylam, DMD</t>
+  </si>
+  <si>
+    <t>(503) 399-9790</t>
+  </si>
+  <si>
+    <t>4455 Sunnyside Rd SE, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday9 AM–2 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; FridayClosed; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dustin+A.+Wylam,+DMD/data=!4m7!3m6!1s0x54bfff686525845f:0x43ddc0d71a0ab6a1!8m2!3d44.890343!4d-123.0357267!16s%2Fg%2F1tdxd_tz!19sChIJX4QlZWj_v1QRobYKGtfA3UM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:04.176Z</t>
+  </si>
+  <si>
+    <t>Bright View Family Dental</t>
+  </si>
+  <si>
+    <t>(971) 707-4983</t>
+  </si>
+  <si>
+    <t>1251 Lancaster Dr NE #A, Salem, OR 97301</t>
+  </si>
+  <si>
+    <t>Closed · Opens 9 AM Mon · See more hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+View+Family+Dental/data=!4m7!3m6!1s0x54bfff42cd59dc9b:0x20194cf60a2186b1!8m2!3d44.9458597!4d-122.9839822!16s%2Fg%2F11j4vrdqbg!19sChIJm9xZzUL_v1QRsYYhCvZMGSA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:33.270Z</t>
+  </si>
+  <si>
+    <t>Salem Heights Dental LLC: Li Biao DDS</t>
+  </si>
+  <si>
+    <t>(503) 364-7776</t>
+  </si>
+  <si>
+    <t>120 Mize Rd SE, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Salem+Heights+Dental+LLC:+Li+Biao+DDS/data=!4m7!3m6!1s0x54c00737106415bf:0x3cc4120d61062aab!8m2!3d44.8940569!4d-123.0569317!16s%2Fg%2F1261by_08!19sChIJvxVkEDcHwFQRqyoGYQ0SxDw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:34.909Z</t>
+  </si>
+  <si>
+    <t>Dr. Benjamin L. Hunsaker, DMD</t>
+  </si>
+  <si>
+    <t>(503) 877-1598</t>
+  </si>
+  <si>
+    <t>1595 Commercial St SE, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Benjamin+L.+Hunsaker,+DMD/data=!4m7!3m6!1s0x54bfff5dc630bd5b:0xd71896d3c3cf240b!8m2!3d44.925451!4d-123.044754!16s%2Fg%2F1tcw3bbv!19sChIJW70wxl3_v1QRCyTPw9OWGNc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:48:36.801Z</t>
+  </si>
+  <si>
+    <t>Chosen Glow Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(503) 507-4513</t>
+  </si>
+  <si>
+    <t>223 Commercial St NE, Salem, OR 97301</t>
+  </si>
+  <si>
+    <t>Sunday4–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chosen+Glow+Teeth+Whitening/data=!4m7!3m6!1s0x54bfff026ba04cf1:0x9fdde2f688ac149a!8m2!3d44.9418706!4d-123.0399495!16s%2Fg%2F11zkwpb8ps!19sChIJ8UygawL_v1QRmhSsiPbi3Z8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:05.291Z</t>
+  </si>
+  <si>
+    <t>Dr. JILA Bowman, DDS</t>
+  </si>
+  <si>
+    <t>(503) 370-4312</t>
+  </si>
+  <si>
+    <t>2300 Lancaster Dr NE, Salem, OR 97305</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+JILA+Bowman,+DDS/data=!4m7!3m6!1s0x54bffe8debcb592f:0x8995a8668f5db9cf!8m2!3d44.9570964!4d-122.9827289!16s%2Fg%2F1vpq6m5c!19sChIJL1nL643-v1QRz7ldj2aolYk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:23.368Z</t>
+  </si>
+  <si>
+    <t>Hearthstone Dental</t>
+  </si>
+  <si>
+    <t>(971) 600-2006</t>
+  </si>
+  <si>
+    <t>3295 Triangle Dr SE #242, Salem, OR 97302</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hearthstone+Dental/data=!4m7!3m6!1s0x54c000a55de96b41:0x8a3c926685e56996!8m2!3d44.9085935!4d-123.0458409!16s%2Fg%2F1tdz94cq!19sChIJQWvpXaUAwFQRlmnlhWaSPIo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:25.280Z</t>
+  </si>
+  <si>
+    <t>Oregon Dental Care</t>
+  </si>
+  <si>
+    <t>(541) 607-7800</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>1800 Valley River Dr, Eugene, OR 97401</t>
+  </si>
+  <si>
+    <t>Eugene</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Oregon+Dental+Care/data=!4m7!3m6!1s0x54c11de58ce8ced7:0x6150a7b9fef66c02!8m2!3d44.070663!4d-123.1090568!16s%2Fg%2F1tvw4nmc!19sChIJ187ojOUdwVQRAmz2_rmnUGE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:49:39.139Z</t>
+  </si>
+  <si>
+    <t>Cal Young Family Dental</t>
+  </si>
+  <si>
+    <t>(541) 357-4938</t>
+  </si>
+  <si>
+    <t>family dentistry</t>
+  </si>
+  <si>
+    <t>1310 Coburg Rd #2, Eugene, OR 97401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cal+Young+Family+Dental/data=!4m7!3m6!1s0x54c0e3004c34dfe7:0x6441b4fcb20fae17!8m2!3d44.0764922!4d-123.0700499!16s%2Fg%2F11m5d67h0k!19sChIJ5980TADjwFQRF64Psvy0QWQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:51:29.993Z</t>
+  </si>
+  <si>
+    <t>Dr. James E. Barta, DDS</t>
+  </si>
+  <si>
+    <t>(541) 345-4076</t>
+  </si>
+  <si>
+    <t>2215 Willamette St Ste B, Eugene, OR 97405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+James+E.+Barta,+DDS/data=!4m7!3m6!1s0x54c11e4fe422a349:0x76d4a8bda2fefdae!8m2!3d44.0352917!4d-123.090834!16s%2Fg%2F1tffjhm3!19sChIJSaMi5E8ewVQRrv3-or2o1HY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:52:06.011Z</t>
+  </si>
+  <si>
+    <t>Drew Katrina DDS</t>
+  </si>
+  <si>
+    <t>(541) 686-2446</t>
+  </si>
+  <si>
+    <t>748 Goodpasture Island Rd, Eugene, OR 97401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Drew+Katrina+DDS/data=!4m7!3m6!1s0x54c11dfb5aecfa0d:0xc5690da5ea7cb64b!8m2!3d44.0852279!4d-123.1100082!16s%2Fg%2F1v2ppyl0!19sChIJDfrsWvsdwVQRS7Z86qUNacU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:52:07.765Z</t>
+  </si>
+  <si>
+    <t>Post Sarah P DMD</t>
+  </si>
+  <si>
+    <t>(541) 271-2758</t>
+  </si>
+  <si>
+    <t>1740 W 17th Ave, Eugene, OR 97402</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Post+Sarah+P+DMD/data=!4m7!3m6!1s0x54c3c3ba0c2dea7b:0x4e5dde8d90dc373b!8m2!3d44.0410051!4d-123.1188325!16s%2Fg%2F1261j3ptc!19sChIJe-otDLrDw1QROzfckI3eXU4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:52:11.227Z</t>
+  </si>
+  <si>
+    <t>Oregon Dental Implants</t>
+  </si>
+  <si>
+    <t>(541) 686-9897</t>
+  </si>
+  <si>
+    <t>1241 Oak St #3519, Eugene, OR 97401</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Oregon+Dental+Implants/data=!4m7!3m6!1s0x54c11e402104481b:0xa855b12eeb1f18b4!8m2!3d44.0462007!4d-123.0909024!16s%2Fg%2F11c1vjwm0c!19sChIJG0gEIUAewVQRtBgf6y6xVag?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:52:36.843Z</t>
+  </si>
+  <si>
+    <t>Santa Clara Dental &amp; Implants</t>
+  </si>
+  <si>
+    <t>(541) 345-0004</t>
+  </si>
+  <si>
+    <t>95 Division Ave, Eugene, OR 97404</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Santa+Clara+Dental+%26+Implants/data=!4m7!3m6!1s0x54c11d23a1d18149:0x1c3c4980cd2d1fa0!8m2!3d44.0994573!4d-123.1259298!16s%2Fg%2F11j43fn35h!19sChIJSYHRoSMdwVQRoB8tzYBJPBw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:52:53.142Z</t>
+  </si>
+  <si>
+    <t>Dental Assist</t>
+  </si>
+  <si>
+    <t>(502) 236-5838</t>
+  </si>
+  <si>
+    <t>852 Beltline Rd, Springfield, OR 97477</t>
+  </si>
+  <si>
+    <t>Springfield</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Assist/data=!4m7!3m6!1s0x54c0e3042c2ba4b9:0x12cba7db11170f97!8m2!3d44.0851989!4d-123.0403123!16s%2Fg%2F11zxckmhpv!19sChIJuaQrLATjwFQRlw8XEdunyxI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:53:17.003Z</t>
+  </si>
+  <si>
+    <t>Dr. Priya I. Bhavan, DDS</t>
+  </si>
+  <si>
+    <t>(541) 345-2042</t>
+  </si>
+  <si>
+    <t>1680 Chambers St #204, Eugene, OR 97402</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Priya+I.+Bhavan,+DDS/data=!4m7!3m6!1s0x54c11e8a0ac54ac7:0xce989d69d72a5b09!8m2!3d44.0416276!4d-123.1179974!16s%2Fg%2F1vzv3d4r!19sChIJx0rFCooewVQRCVsq12mdmM4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:53:18.864Z</t>
+  </si>
+  <si>
+    <t>Bumstead Martin DDS</t>
+  </si>
+  <si>
+    <t>(541) 687-2343</t>
+  </si>
+  <si>
+    <t>3467 Hilyard St, Eugene, OR 97405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bumstead+Martin+DDS/data=!4m7!3m6!1s0x54c11fa61ec27c15:0x9a07a92695eb2cf0!8m2!3d44.018778!4d-123.080957!16s%2Fg%2F1tn00z6y!19sChIJFXzCHqYfwVQR8CzrlSapB5o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:53:20.865Z</t>
+  </si>
+  <si>
+    <t>CC Dental Help</t>
+  </si>
+  <si>
+    <t>(541) 357-8164</t>
+  </si>
+  <si>
+    <t>2964 Dahlia Ln, Eugene, OR 97404</t>
+  </si>
+  <si>
+    <t>Sunday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CC+Dental+Help/data=!4m7!3m6!1s0x54c11d603671fb0d:0xd2cb3132318f7814!8m2!3d44.107311!4d-123.1416061!16s%2Fg%2F11b727x4xj!19sChIJDftxNmAdwVQRFHiPMTIxy9I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:53:23.763Z</t>
+  </si>
+  <si>
+    <t>Ba'yoami Beauty Parlour &amp; Spa LLC</t>
+  </si>
+  <si>
+    <t>(458) 210-9806</t>
+  </si>
+  <si>
+    <t>Health spa</t>
+  </si>
+  <si>
+    <t>379 Coburg Rd, Eugene, OR 97401</t>
+  </si>
+  <si>
+    <t>Sunday8:30 AM–8:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ba%27yoami+Beauty+Parlour+%26+Spa+LLC/data=!4m7!3m6!1s0x54c0e10a42018dc7:0x5cd4f29026bde08e!8m2!3d44.0664382!4d-123.072595!16s%2Fg%2F11fqc7g_yp!19sChIJx40BQgrhwFQRjuC9JpDy1Fw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:11.182Z</t>
+  </si>
+  <si>
+    <t>East County Health Center</t>
+  </si>
+  <si>
+    <t>(503) 988-5155</t>
+  </si>
+  <si>
+    <t>Public health department</t>
+  </si>
+  <si>
+    <t>600 NE 8th St #300, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>Gresham</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/East+County+Health+Center/data=!4m7!3m6!1s0x5495985ffd2ae51b:0xa845a23da4214e52!8m2!3d45.5026597!4d-122.4252006!16s%2Fg%2F1w3469y6!19sChIJG-Uq_V-YlVQRUk4hpD2iRag?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:31.744Z</t>
+  </si>
+  <si>
+    <t>Care Source Dental</t>
+  </si>
+  <si>
+    <t>(470) 665-1660</t>
+  </si>
+  <si>
+    <t>236 NE Roberts Ave, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Care+Source+Dental/data=!4m7!3m6!1s0x549599eda6bc6de1:0xf978a308467ad405!8m2!3d45.4995191!4d-122.4294571!16s%2Fg%2F11w25q8qv3!19sChIJ4W28pu2ZlVQRBdR6RgijePk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:36.826Z</t>
+  </si>
+  <si>
+    <t>Dr. Gary S. Cooke, DMD</t>
+  </si>
+  <si>
+    <t>(503) 665-6166</t>
+  </si>
+  <si>
+    <t>490 E Powell Blvd, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gary+S.+Cooke,+DMD/data=!4m7!3m6!1s0x549598f42ffde35d:0xafcddcd305127861!8m2!3d45.4977845!4d-122.4262055!16s%2Fg%2F1v9gv558!19sChIJXeP9L_SYlVQRYXgSBdPcza8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:38.654Z</t>
+  </si>
+  <si>
+    <t>Dr. Joshua Kim</t>
+  </si>
+  <si>
+    <t>(503) 492-7798</t>
+  </si>
+  <si>
+    <t>1024 SW Highland Dr, Gresham, OR 97080</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joshua+Kim/data=!4m7!3m6!1s0x549598b5b7f30001:0xfdee2794d227a28d!8m2!3d45.4891003!4d-122.4747732!16s%2Fg%2F11ty7v0n_j!19sChIJAQDzt7WYlVQRjaIn0pQn7v0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:40.259Z</t>
+  </si>
+  <si>
+    <t>Adventist Health Med Clinic</t>
+  </si>
+  <si>
+    <t>(503) 665-8176</t>
+  </si>
+  <si>
+    <t>831 NW Council Dr Unit 101, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Adventist+Health+Med+Clinic/data=!4m7!3m6!1s0x54959887a84e60ad:0x60cc90939274cea6!8m2!3d45.5104746!4d-122.4401708!16s%2Fg%2F1vrq9bpg!19sChIJrWBOqIeYlVQRps50kpOQzGA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:42.443Z</t>
+  </si>
+  <si>
+    <t>Multnomah County- East County Health Center (parking lot)</t>
+  </si>
+  <si>
+    <t>(503) 988-8939</t>
+  </si>
+  <si>
+    <t>Community health center</t>
+  </si>
+  <si>
+    <t>600 NE 8th St, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Multnomah+County-+East+County+Health+Center+%28parking+lot%29/data=!4m7!3m6!1s0x5495985fe3400001:0xea7c6c4b68f25550!8m2!3d45.5025983!4d-122.4250467!16s%2Fg%2F11jy7svlnt!19sChIJAQBA41-YlVQRUFXyaEtsfOo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:44.651Z</t>
+  </si>
+  <si>
+    <t>Athena Bettger</t>
+  </si>
+  <si>
+    <t>(503) 988-4900</t>
+  </si>
+  <si>
+    <t>DENTAL CLINIC, 600 NE 8th St, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Athena+Bettger/data=!4m7!3m6!1s0x5495985fe3400001:0x642ac97a725320d4!8m2!3d45.5026424!4d-122.4251079!16s%2Fg%2F11pkfr6225!19sChIJAQBA41-YlVQR1CBTcnrJKmQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:54:46.379Z</t>
+  </si>
+  <si>
+    <t>Dr. Summer A. Archibald, DDS</t>
+  </si>
+  <si>
+    <t>(503) 661-2600</t>
+  </si>
+  <si>
+    <t>2150 NE Division St #201, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Summer+A.+Archibald,+DDS/data=!4m7!3m6!1s0x549598f52c24c5cd:0xb03974d5fd6a4109!8m2!3d45.504177!4d-122.4107879!16s%2Fg%2F1tc_3t8r!19sChIJzcUkLPWYlVQRCUFq_dV0ObA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:55:46.982Z</t>
+  </si>
+  <si>
+    <t>Comfort Dentistry</t>
+  </si>
+  <si>
+    <t>(503) 674-9900</t>
+  </si>
+  <si>
+    <t>829 SE 182nd Ave #100, Portland, OR 97233</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Comfort+Dentistry/data=!4m7!3m6!1s0x5495a272fb1afa47:0xd775aa5c726691a1!8m2!3d45.5163264!4d-122.4762!16s%2Fg%2F1tjg_1y5!19sChIJR_oa-3KilVQRoZFmclyqddc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:55:53.418Z</t>
+  </si>
+  <si>
+    <t>Whiten My Smile Teeth Whitening Services</t>
+  </si>
+  <si>
+    <t>(503) 928-4877</t>
+  </si>
+  <si>
+    <t>Cosmetic dentist</t>
+  </si>
+  <si>
+    <t>219 NW 1st St, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Whiten+My+Smile+Teeth+Whitening+Services/data=!4m7!3m6!1s0x549598f31eaec591:0x9fccfa7aca470352!8m2!3d45.4984304!4d-122.4338418!16s%2Fg%2F11xbtjldn!19sChIJkcWuHvOYlVQRUgNHynr6zJ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:56:41.937Z</t>
+  </si>
+  <si>
+    <t>Dr. Jiyoung E. Lee, DMD</t>
+  </si>
+  <si>
+    <t>(503) 666-9436</t>
+  </si>
+  <si>
+    <t>831 NW Council Dr #210, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jiyoung+E.+Lee,+DMD/data=!4m7!3m6!1s0x5495985cd24a025d:0xa51ef5a076cabbfc!8m2!3d45.5108601!4d-122.4401366!16s%2Fg%2F1vxdx_dt!19sChIJXQJK0lyYlVQR_LvKdqD1HqU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:56:51.628Z</t>
+  </si>
+  <si>
+    <t>Dental Match</t>
+  </si>
+  <si>
+    <t>(503) 974-3725</t>
+  </si>
+  <si>
+    <t>327 N Main Ave, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Match/data=!4m7!3m6!1s0x549599c73e4e596b:0x2a1085c874ecd5d2!8m2!3d45.5001316!4d-122.4313823!16s%2Fg%2F11zxck24_z!19sChIJa1lOPseZlVQR0tXsdMiFECo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:57:26.033Z</t>
+  </si>
+  <si>
+    <t>Dr. Angie A. Rawley, DMD</t>
+  </si>
+  <si>
+    <t>(503) 666-8045</t>
+  </si>
+  <si>
+    <t>2458 SE Burnside Rd, Gresham, OR 97080</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Angie+A.+Rawley,+DMD/data=!4m7!3m6!1s0x5495985129a67083:0xd03bd5b1263c1a26!8m2!3d45.4949397!4d-122.4083131!16s%2Fg%2F113fnxgg2!19sChIJg3CmKVGYlVQRJho8JrHVO9A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:57:30.875Z</t>
+  </si>
+  <si>
+    <t>Gresham Downtown Dental Group: Underwood Lori</t>
+  </si>
+  <si>
+    <t>(503) 666-5484</t>
+  </si>
+  <si>
+    <t>315 NW Burnside Rd, Gresham, OR 97030</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gresham+Downtown+Dental+Group:+Underwood+Lori/data=!4m7!3m6!1s0x549598f5228f767f:0x99e7d331da6124a8!8m2!3d45.5008089!4d-122.427665!16s%2Fg%2F1tfs0skc!19sChIJf3aPIvWYlVQRqCRh2jHT55k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T18:57:56.098Z</t>
+  </si>
+  <si>
+    <t>Lester Laraway, DDS</t>
+  </si>
+  <si>
+    <t>(503) 286-6868</t>
+  </si>
+  <si>
+    <t>19075 NW Tanasbourne Dr, Hillsboro, OR 97124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lester+Laraway,+DDS/data=!4m7!3m6!1s0x54950f5dc71d89bd:0x3f5523ec84456991!8m2!3d45.5422488!4d-122.8733868!16s%2Fg%2F1tv23w2d!19sChIJvYkdx10PlVQRkWlFhOwjVT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:00:52.410Z</t>
+  </si>
+  <si>
+    <t>Dr. Tess Gladstone</t>
+  </si>
+  <si>
+    <t>(503) 693-6163</t>
+  </si>
+  <si>
+    <t>434 S 1st Ave Ste 300, Hillsboro, OR 97123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tess+Gladstone/data=!4m7!3m6!1s0x54951aa267b00001:0xebc0edcf31bcd73a!8m2!3d45.5184276!4d-122.9895754!16s%2Fg%2F11rwxg5h2c!19sChIJAQCwZ6IalVQROte8Mc_twOs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:00:55.733Z</t>
+  </si>
+  <si>
+    <t>Shao-Chiu Chen</t>
+  </si>
+  <si>
+    <t>(503) 644-4749</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>3075 SE Century Blvd Ste 109, Hillsboro, OR 97123</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Shao-Chiu+Chen/data=!4m7!3m6!1s0x54950fd41ccd3d55:0x2b89e945767fdd30!8m2!3d45.4967877!4d-122.9190829!16s%2Fg%2F11s622lhp8!19sChIJVT3NHNQPlVQRMN1_dkXpiSs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:01:13.972Z</t>
+  </si>
+  <si>
+    <t>Dr. Charles M. Buxton, DMD</t>
+  </si>
+  <si>
+    <t>(503) 924-2248</t>
+  </si>
+  <si>
+    <t>5625 NE Elam Young Pkwy Ste 300, Hillsboro, OR 97124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Charles+M.+Buxton,+DMD/data=!4m7!3m6!1s0x54950f89bf23aca1:0x7f429f64a23729e7!8m2!3d45.5313107!4d-122.9230073!16s%2Fg%2F1vqtghjh!19sChIJoawjv4kPlVQR5yk3omSfQn8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:01:17.980Z</t>
+  </si>
+  <si>
+    <t>Michael Matsuda</t>
+  </si>
+  <si>
+    <t>(503) 640-1313</t>
+  </si>
+  <si>
+    <t>363 SE 4th Ave, Hillsboro, OR 971234281</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+Matsuda/data=!4m7!3m6!1s0x54951aa3ed315555:0xbf2605e309690237!8m2!3d45.5191689!4d-122.9847878!16s%2Fg%2F11sh2c8wjv!19sChIJVVUx7aMalVQRNwJpCeMFJr8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:01:26.061Z</t>
+  </si>
+  <si>
+    <t>Dr. Anthony Adams</t>
+  </si>
+  <si>
+    <t>(503) 646-9772</t>
+  </si>
+  <si>
+    <t>5880 NE Cornell Rd Ste A, Hillsboro, OR 97124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Anthony+Adams/data=!4m7!3m6!1s0x54950562a4255555:0xfb5e7f125edff7ba!8m2!3d45.5335117!4d-122.9213829!16s%2Fg%2F11qgb742fd!19sChIJVVUlpGIFlVQRuvffXhJ_Xvs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:00.959Z</t>
+  </si>
+  <si>
+    <t>Beaverton Sandy Dental Clinic PC</t>
+  </si>
+  <si>
+    <t>(503) 646-5230</t>
+  </si>
+  <si>
+    <t>12520 SW 1st St, Beaverton, OR 97005</t>
+  </si>
+  <si>
+    <t>Beaverton</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Beaverton+Sandy+Dental+Clinic+PC/data=!4m7!3m6!1s0x54950c20091c9271:0x387d2b457f7c3084!8m2!3d45.4861733!4d-122.8054437!16s%2Fg%2F1tg34y89!19sChIJcZIcCSAMlVQRhDB8f0UrfTg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:41.007Z</t>
+  </si>
+  <si>
+    <t>Cherry Dental</t>
+  </si>
+  <si>
+    <t>(503) 644-1110</t>
+  </si>
+  <si>
+    <t>8070 SW Hall Blvd #200, Beaverton, OR 97008</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cherry+Dental/data=!4m7!3m6!1s0x54950d2b1b9a5b13:0xd3376b8257de3c9a!8m2!3d45.4615831!4d-122.7962807!16s%2Fg%2F11h0_d71pw!19sChIJE1uaGysNlVQRmjzeV4JrN9M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:42.993Z</t>
+  </si>
+  <si>
+    <t>Thomas Family Dentistry</t>
+  </si>
+  <si>
+    <t>(503) 644-7697</t>
+  </si>
+  <si>
+    <t>12575 SW 3rd St, Beaverton, OR 97005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thomas+Family+Dentistry/data=!4m7!3m6!1s0x54950c2066f46ab9:0x80bc3047184646e5!8m2!3d45.4851741!4d-122.8058642!16s%2Fg%2F1v8gbr4x!19sChIJuWr0ZiAMlVQR5UZGGEcwvIA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:45.117Z</t>
+  </si>
+  <si>
+    <t>Aloha Dental Specialty Center</t>
+  </si>
+  <si>
+    <t>(503) 822-0096</t>
+  </si>
+  <si>
+    <t>18455 SW Alexander St Ste B, Beaverton, OR 97003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aloha+Dental+Specialty+Center/data=!4m7!3m6!1s0x54950fa3e17f55ab:0x5f6b3043fdb2d7f4!8m2!3d45.4953776!4d-122.86683!16s%2Fg%2F11z8kzxx5x!19sChIJq1V_4aMPlVQR9Ney_UMwa18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:46.947Z</t>
+  </si>
+  <si>
+    <t>Elmonica Dental</t>
+  </si>
+  <si>
+    <t>(503) 629-2222</t>
+  </si>
+  <si>
+    <t>17020 SW Whitley Way #101, Beaverton, OR 97006</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Elmonica+Dental/data=!4m7!3m6!1s0x54950ee2869f0841:0xfd8a6414e7aa74f9!8m2!3d45.512803!4d-122.8522602!16s%2Fg%2F1v27v69t!19sChIJQQifhuIOlVQR-XSq5xRkiv0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:02:49.390Z</t>
+  </si>
+  <si>
+    <t>Nevills Family Dentistry</t>
+  </si>
+  <si>
+    <t>(503) 649-3232</t>
+  </si>
+  <si>
+    <t>18540 SW Vincent St, Aloha, OR 97007</t>
+  </si>
+  <si>
+    <t>Aloha</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Nevills+Family+Dentistry/data=!4m7!3m6!1s0x54950e420d03b253:0x7eed4502db691f50!8m2!3d45.4876806!4d-122.8676256!16s%2Fg%2F1tcw7x1y!19sChIJU7IDDUIOlVQRUB9p2wJF7X4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:03:59.168Z</t>
+  </si>
+  <si>
+    <t>Dr. Stephanie Wold-Christensen</t>
+  </si>
+  <si>
+    <t>(541) 389-3073</t>
+  </si>
+  <si>
+    <t>1475 SW Chandler Ave #202, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>Bend</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Stephanie+Wold-Christensen/data=!4m7!3m6!1s0x54b8c7db2bc9cbff:0xf68fbdb470d8afc6!8m2!3d44.0419964!4d-121.3339683!16s%2Fg%2F11tn9k7n70!19sChIJ_8vJK9vHuFQRxq_YcLS9j_Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:06.840Z</t>
+  </si>
+  <si>
+    <t>Align Orthodontics</t>
+  </si>
+  <si>
+    <t>(503) 362-0500</t>
+  </si>
+  <si>
+    <t>2955 N Hwy 97, Bend, OR 97703</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Align+Orthodontics/data=!4m7!3m6!1s0x54b8c61f7ffd459d:0x8e820b02388926ec!8m2!3d44.079043!4d-121.3053283!16s%2Fg%2F11dxkc5g6c!19sChIJnUX9fx_GuFQR7CaJOAILgo4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:19.958Z</t>
+  </si>
+  <si>
+    <t>Burnside Orthodontics: Burnside Robert E DDS</t>
+  </si>
+  <si>
+    <t>(541) 382-5766</t>
+  </si>
+  <si>
+    <t>551 NE Greenwood Ave, Bend, OR 97701</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Burnside+Orthodontics:+Burnside+Robert+E+DDS/data=!4m7!3m6!1s0x54b8c61f6d8423db:0x87cfc7902831bbdc!8m2!3d44.059641!4d-121.2978493!16s%2Fg%2F1whdj1zj!19sChIJ2yOEbR_GuFQR3LsxKJDHz4c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:22.045Z</t>
+  </si>
+  <si>
+    <t>Bend Implant Dentist</t>
+  </si>
+  <si>
+    <t>(541) 389-2885</t>
+  </si>
+  <si>
+    <t>1470 SW Knoll Ave #103, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bend+Implant+Dentist/data=!4m7!3m6!1s0x54b8c7d66a0d7a47:0x85eb2673bdfd8e1e!8m2!3d44.0505304!4d-121.3333186!16s%2Fg%2F11bzrg1dp8!19sChIJR3oNatbHuFQRHo79vXMm64U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:38.928Z</t>
+  </si>
+  <si>
+    <t>JTurner DMD, LLC</t>
+  </si>
+  <si>
+    <t>(541) 389-7257</t>
+  </si>
+  <si>
+    <t>300 SW Columbia St Ste 102, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/JTurner+DMD,+LLC/data=!4m7!3m6!1s0x54b8c7d3d9ed93d7:0xd21be5dd03e5cfc8!8m2!3d44.0471808!4d-121.3267064!16s%2Fg%2F11cjhjm8vp!19sChIJ15Pt2dPHuFQRyM_lA93lG9I?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:41.412Z</t>
+  </si>
+  <si>
+    <t>Mirror Pond Dental</t>
+  </si>
+  <si>
+    <t>(541) 382-2256</t>
+  </si>
+  <si>
+    <t>102 NW Newport Ave, Bend, OR 97701</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mirror+Pond+Dental/data=!4m7!3m6!1s0x54b8c89c63c2df27:0x3f21b8cf9b218540!8m2!3d44.06155!4d-121.3146793!16s%2Fg%2F1v830v66!19sChIJJ9_CY5zIuFQRQIUhm8-4IT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:43.358Z</t>
+  </si>
+  <si>
+    <t>Dentist Bend Oregon</t>
+  </si>
+  <si>
+    <t>(888) 422-8201</t>
+  </si>
+  <si>
+    <t>70 SW Century Dr, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Bend+Oregon/data=!4m7!3m6!1s0x54b8c7d5d2353e65:0x82823b7a53bc1edb!8m2!3d44.0505409!4d-121.3305506!16s%2Fg%2F11r8dy1pv!19sChIJZT410tXHuFQR2x68U3o7goI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:08:45.413Z</t>
+  </si>
+  <si>
+    <t>Radiant Smiles Studio</t>
+  </si>
+  <si>
+    <t>(541) 204-0866</t>
+  </si>
+  <si>
+    <t>61396 S Hwy 97 Ste 102, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Radiant+Smiles+Studio/data=!4m7!3m6!1s0x54b8c7989622d4db:0xd7b29bfbb2a55746!8m2!3d44.0294777!4d-121.3109786!16s%2Fg%2F11ybnhr4b8!19sChIJ29QilpjHuFQRRlelsvubstc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:09:38.470Z</t>
+  </si>
+  <si>
+    <t>Dr. Tad W. Burzynski, DDS</t>
+  </si>
+  <si>
+    <t>(541) 389-7485</t>
+  </si>
+  <si>
+    <t>853 NE 4th St, Bend, OR 97701</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tad+W.+Burzynski,+DDS/data=!4m7!3m6!1s0x54b8c621b9c97a1b:0xbcad4d8f7b499f82!8m2!3d44.0588093!4d-121.3009292!16s%2Fg%2F1tdk09fh!19sChIJG3rJuSHGuFQRgp9Je49Nrbw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:09:53.820Z</t>
+  </si>
+  <si>
+    <t>Steven D Apfelbaum PC</t>
+  </si>
+  <si>
+    <t>(541) 382-5080</t>
+  </si>
+  <si>
+    <t>1569 SW Nancy Way #3, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Steven+D+Apfelbaum+PC/data=!4m7!3m6!1s0x54b8c7db5135f909:0xa1eb80a683befe5e!8m2!3d44.0413836!4d-121.3365468!16s%2Fg%2F1tjynfsj!19sChIJCfk1UdvHuFQRXv6-g6aA66E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:09:55.782Z</t>
+  </si>
+  <si>
+    <t>Healthy Bend Dental Implant Center</t>
+  </si>
+  <si>
+    <t>(541) 382-6565</t>
+  </si>
+  <si>
+    <t>225 SW Scalehouse Loop, Bend, OR 97702</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Healthy+Bend+Dental+Implant+Center/data=!4m7!3m6!1s0x54b8c631ff2c956d:0x36c6810b148d50e7!8m2!3d44.0483489!4d-121.3112857!16s%2Fg%2F11g6rjkjy0!19sChIJbZUs_zHGuFQR51CNFAuBxjY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T19:09:58.199Z</t>
   </si>
 </sst>
 </file>
@@ -748,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1462,6 +2404,2302 @@
         <v>118</v>
       </c>
     </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>131</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>138</v>
+      </c>
+      <c r="M20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>148</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>149</v>
+      </c>
+      <c r="M22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>156</v>
+      </c>
+      <c r="M23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>168</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>169</v>
+      </c>
+      <c r="M25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>30</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>175</v>
+      </c>
+      <c r="M26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>179</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>185</v>
+      </c>
+      <c r="M28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>190</v>
+      </c>
+      <c r="M29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" t="s">
+        <v>167</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>195</v>
+      </c>
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>196</v>
+      </c>
+      <c r="M30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>198</v>
+      </c>
+      <c r="B31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>201</v>
+      </c>
+      <c r="M31" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" t="s">
+        <v>79</v>
+      </c>
+      <c r="D32" t="s">
+        <v>205</v>
+      </c>
+      <c r="E32" t="s">
+        <v>206</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>207</v>
+      </c>
+      <c r="M32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>211</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>56</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>167</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" t="s">
+        <v>222</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>223</v>
+      </c>
+      <c r="M35" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s">
+        <v>229</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>230</v>
+      </c>
+      <c r="M36" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37" t="s">
+        <v>234</v>
+      </c>
+      <c r="D37" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" t="s">
+        <v>236</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I37" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>237</v>
+      </c>
+      <c r="M37" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>239</v>
+      </c>
+      <c r="B38" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" t="s">
+        <v>241</v>
+      </c>
+      <c r="E38" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>56</v>
+      </c>
+      <c r="I38" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>242</v>
+      </c>
+      <c r="M38" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>246</v>
+      </c>
+      <c r="E39" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>247</v>
+      </c>
+      <c r="M39" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>56</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>252</v>
+      </c>
+      <c r="M40" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>255</v>
+      </c>
+      <c r="C41" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" t="s">
+        <v>256</v>
+      </c>
+      <c r="E41" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>257</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>56</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>258</v>
+      </c>
+      <c r="M41" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>260</v>
+      </c>
+      <c r="B42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E42" t="s">
+        <v>236</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>264</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>265</v>
+      </c>
+      <c r="M42" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>267</v>
+      </c>
+      <c r="B43" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>269</v>
+      </c>
+      <c r="E43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>56</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>270</v>
+      </c>
+      <c r="M43" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>272</v>
+      </c>
+      <c r="B44" t="s">
+        <v>273</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>274</v>
+      </c>
+      <c r="E44" t="s">
+        <v>236</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>116</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>30</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>275</v>
+      </c>
+      <c r="M44" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>277</v>
+      </c>
+      <c r="B45" t="s">
+        <v>278</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>279</v>
+      </c>
+      <c r="E45" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>280</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>281</v>
+      </c>
+      <c r="M45" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>283</v>
+      </c>
+      <c r="B46" t="s">
+        <v>284</v>
+      </c>
+      <c r="C46" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" t="s">
+        <v>286</v>
+      </c>
+      <c r="E46" t="s">
+        <v>236</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" t="s">
+        <v>86</v>
+      </c>
+      <c r="J46" t="s">
+        <v>56</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>287</v>
+      </c>
+      <c r="M46" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>289</v>
+      </c>
+      <c r="B47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C47" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" t="s">
+        <v>291</v>
+      </c>
+      <c r="E47" t="s">
+        <v>236</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>123</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>292</v>
+      </c>
+      <c r="M47" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48" t="s">
+        <v>295</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
+        <v>296</v>
+      </c>
+      <c r="E48" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>56</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>297</v>
+      </c>
+      <c r="M48" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>301</v>
+      </c>
+      <c r="E49" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>56</v>
+      </c>
+      <c r="I49" t="s">
+        <v>86</v>
+      </c>
+      <c r="J49" t="s">
+        <v>56</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>302</v>
+      </c>
+      <c r="M49" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>304</v>
+      </c>
+      <c r="B50" t="s">
+        <v>305</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" t="s">
+        <v>236</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>56</v>
+      </c>
+      <c r="I50" t="s">
+        <v>86</v>
+      </c>
+      <c r="J50" t="s">
+        <v>30</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>307</v>
+      </c>
+      <c r="M50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>309</v>
+      </c>
+      <c r="B51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>312</v>
+      </c>
+      <c r="M51" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>314</v>
+      </c>
+      <c r="B52" t="s">
+        <v>315</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>316</v>
+      </c>
+      <c r="E52" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>56</v>
+      </c>
+      <c r="I52" t="s">
+        <v>86</v>
+      </c>
+      <c r="J52" t="s">
+        <v>56</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>317</v>
+      </c>
+      <c r="M52" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D53" t="s">
+        <v>322</v>
+      </c>
+      <c r="E53" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>56</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>323</v>
+      </c>
+      <c r="M53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+      <c r="C54" t="s">
+        <v>321</v>
+      </c>
+      <c r="D54" t="s">
+        <v>327</v>
+      </c>
+      <c r="E54" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>56</v>
+      </c>
+      <c r="I54" t="s">
+        <v>86</v>
+      </c>
+      <c r="J54" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>328</v>
+      </c>
+      <c r="M54" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>330</v>
+      </c>
+      <c r="B55" t="s">
+        <v>331</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" t="s">
+        <v>332</v>
+      </c>
+      <c r="E55" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>74</v>
+      </c>
+      <c r="J55" t="s">
+        <v>155</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>333</v>
+      </c>
+      <c r="M55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" t="s">
+        <v>73</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>56</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>338</v>
+      </c>
+      <c r="M56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>342</v>
+      </c>
+      <c r="E57" t="s">
+        <v>343</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>344</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>345</v>
+      </c>
+      <c r="M57" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>347</v>
+      </c>
+      <c r="B58" t="s">
+        <v>348</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" t="s">
+        <v>349</v>
+      </c>
+      <c r="E58" t="s">
+        <v>343</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>48</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>30</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>350</v>
+      </c>
+      <c r="M58" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>352</v>
+      </c>
+      <c r="B59" t="s">
+        <v>353</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" t="s">
+        <v>354</v>
+      </c>
+      <c r="E59" t="s">
+        <v>343</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>30</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>355</v>
+      </c>
+      <c r="M59" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>357</v>
+      </c>
+      <c r="B60" t="s">
+        <v>358</v>
+      </c>
+      <c r="C60" t="s">
+        <v>285</v>
+      </c>
+      <c r="D60" t="s">
+        <v>359</v>
+      </c>
+      <c r="E60" t="s">
+        <v>343</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>30</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>360</v>
+      </c>
+      <c r="M60" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" t="s">
+        <v>364</v>
+      </c>
+      <c r="E61" t="s">
+        <v>343</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>365</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>56</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>366</v>
+      </c>
+      <c r="M61" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>368</v>
+      </c>
+      <c r="B62" t="s">
+        <v>369</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>370</v>
+      </c>
+      <c r="E62" t="s">
+        <v>371</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>30</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>372</v>
+      </c>
+      <c r="M62" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>374</v>
+      </c>
+      <c r="B63" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D63" t="s">
+        <v>376</v>
+      </c>
+      <c r="E63" t="s">
+        <v>377</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>56</v>
+      </c>
+      <c r="I63" t="s">
+        <v>86</v>
+      </c>
+      <c r="J63" t="s">
+        <v>56</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>378</v>
+      </c>
+      <c r="M63" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>380</v>
+      </c>
+      <c r="B64" t="s">
+        <v>381</v>
+      </c>
+      <c r="C64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D64" t="s">
+        <v>382</v>
+      </c>
+      <c r="E64" t="s">
+        <v>377</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>56</v>
+      </c>
+      <c r="I64" t="s">
+        <v>86</v>
+      </c>
+      <c r="J64" t="s">
+        <v>222</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>383</v>
+      </c>
+      <c r="M64" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>385</v>
+      </c>
+      <c r="B65" t="s">
+        <v>386</v>
+      </c>
+      <c r="C65" t="s">
+        <v>321</v>
+      </c>
+      <c r="D65" t="s">
+        <v>387</v>
+      </c>
+      <c r="E65" t="s">
+        <v>377</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>20</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>56</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>388</v>
+      </c>
+      <c r="M65" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>390</v>
+      </c>
+      <c r="B66" t="s">
+        <v>391</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>392</v>
+      </c>
+      <c r="E66" t="s">
+        <v>377</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>56</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>393</v>
+      </c>
+      <c r="M66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>395</v>
+      </c>
+      <c r="B67" t="s">
+        <v>396</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" t="s">
+        <v>397</v>
+      </c>
+      <c r="E67" t="s">
+        <v>377</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s">
+        <v>74</v>
+      </c>
+      <c r="J67" t="s">
+        <v>56</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>398</v>
+      </c>
+      <c r="M67" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>400</v>
+      </c>
+      <c r="B68" t="s">
+        <v>401</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>402</v>
+      </c>
+      <c r="E68" t="s">
+        <v>377</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>403</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>404</v>
+      </c>
+      <c r="M68" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>406</v>
+      </c>
+      <c r="B69" t="s">
+        <v>407</v>
+      </c>
+      <c r="C69" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" t="s">
+        <v>408</v>
+      </c>
+      <c r="E69" t="s">
+        <v>377</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>409</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>30</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>410</v>
+      </c>
+      <c r="M69" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>412</v>
+      </c>
+      <c r="B70" t="s">
+        <v>413</v>
+      </c>
+      <c r="C70" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" t="s">
+        <v>414</v>
+      </c>
+      <c r="E70" t="s">
+        <v>377</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>56</v>
+      </c>
+      <c r="I70" t="s">
+        <v>86</v>
+      </c>
+      <c r="J70" t="s">
+        <v>415</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>416</v>
+      </c>
+      <c r="M70" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>418</v>
+      </c>
+      <c r="B71" t="s">
+        <v>419</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
+        <v>420</v>
+      </c>
+      <c r="E71" t="s">
+        <v>377</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>257</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>56</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>421</v>
+      </c>
+      <c r="M71" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>423</v>
+      </c>
+      <c r="B72" t="s">
+        <v>424</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>425</v>
+      </c>
+      <c r="E72" t="s">
+        <v>377</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>56</v>
+      </c>
+      <c r="I72" t="s">
+        <v>86</v>
+      </c>
+      <c r="J72" t="s">
+        <v>56</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>426</v>
+      </c>
+      <c r="M72" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>428</v>
+      </c>
+      <c r="B73" t="s">
+        <v>429</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>430</v>
+      </c>
+      <c r="E73" t="s">
+        <v>377</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>56</v>
+      </c>
+      <c r="I73" t="s">
+        <v>86</v>
+      </c>
+      <c r="J73" t="s">
+        <v>30</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>431</v>
+      </c>
+      <c r="M73" t="s">
+        <v>432</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
